--- a/CO国試data/CO_questions_2014.xlsx
+++ b/CO国試data/CO_questions_2014.xlsx
@@ -542,15 +542,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>個体の構造</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -635,15 +634,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>True</t>
@@ -821,15 +818,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -914,15 +910,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>False</t>
@@ -1007,15 +1002,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>遺伝</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1100,15 +1094,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1193,15 +1186,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>3</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>True</t>
@@ -1291,14 +1283,10 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>3</v>
       </c>
@@ -1347,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1386,12 +1373,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -1440,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1476,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>4</v>
       </c>
@@ -1533,7 +1519,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1569,15 +1554,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -1626,7 +1611,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1662,15 +1646,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1719,7 +1703,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1755,15 +1738,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>4</v>
       </c>
@@ -1812,7 +1795,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1848,15 +1830,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1905,7 +1887,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1941,15 +1922,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>4</v>
       </c>
@@ -1999,7 +1980,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>False</t>
@@ -2035,15 +2015,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2092,7 +2072,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>True</t>
@@ -2128,15 +2107,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2185,7 +2164,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>False</t>
@@ -2221,15 +2199,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2278,7 +2256,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>False</t>
@@ -2314,15 +2291,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>4</v>
       </c>
@@ -2371,7 +2348,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2407,15 +2383,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>3</v>
       </c>
@@ -2464,7 +2440,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>True</t>
@@ -2500,15 +2475,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -2557,7 +2532,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>False</t>
@@ -2593,15 +2567,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>4</v>
       </c>
@@ -2650,7 +2624,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2686,15 +2659,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>3</v>
       </c>
@@ -2743,7 +2716,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2779,15 +2751,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2836,7 +2808,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2872,15 +2843,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>3</v>
       </c>
@@ -2970,15 +2941,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3027,7 +2998,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3063,15 +3033,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>4</v>
       </c>
@@ -3161,15 +3131,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3218,7 +3188,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>False</t>
@@ -3254,15 +3223,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -3352,15 +3321,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -3409,7 +3378,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>False</t>
@@ -3445,15 +3413,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>4</v>
       </c>
@@ -3502,7 +3470,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>True</t>
@@ -3538,15 +3505,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>3</v>
       </c>
@@ -3595,7 +3562,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>True</t>
@@ -3634,12 +3600,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>1</v>
       </c>
@@ -3688,7 +3654,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>False</t>
@@ -3724,15 +3689,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>2</v>
       </c>
@@ -3781,7 +3746,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>False</t>
@@ -3817,15 +3781,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>4</v>
       </c>
@@ -3874,7 +3838,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3910,15 +3873,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3967,7 +3930,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>True</t>
@@ -4003,15 +3965,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4060,7 +4022,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>False</t>
@@ -4096,15 +4057,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -4153,7 +4114,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>False</t>
@@ -4189,15 +4149,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>3</v>
       </c>
@@ -4246,7 +4206,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4282,15 +4241,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4339,7 +4298,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>False</t>
@@ -4375,15 +4333,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4432,7 +4390,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>False</t>
@@ -4468,15 +4425,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4525,7 +4482,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>False</t>
@@ -4561,15 +4517,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4618,7 +4574,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4654,15 +4609,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4711,7 +4666,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>False</t>
@@ -4747,15 +4701,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -4804,7 +4758,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4840,15 +4793,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4897,7 +4850,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4933,15 +4885,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -4990,7 +4942,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>False</t>
@@ -5026,15 +4977,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>4</v>
       </c>
@@ -5083,7 +5034,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>False</t>
@@ -5119,15 +5069,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -5176,7 +5126,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>False</t>
@@ -5212,15 +5161,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5269,7 +5218,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>False</t>
@@ -5305,15 +5253,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>4</v>
       </c>
@@ -5403,15 +5351,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>4</v>
       </c>
@@ -5460,7 +5408,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>False</t>
@@ -5496,15 +5443,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>4</v>
       </c>
@@ -5553,7 +5500,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>False</t>
@@ -5589,15 +5535,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>3</v>
       </c>
@@ -5646,7 +5592,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>False</t>
@@ -5682,15 +5627,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5780,15 +5725,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>2</v>
       </c>
@@ -5837,7 +5782,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>False</t>
@@ -5873,19 +5817,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
+          <t>視能訓練学</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5934,7 +5874,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>False</t>
@@ -5970,15 +5909,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -6027,7 +5966,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>True</t>
@@ -6063,15 +6001,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>4</v>
       </c>
@@ -6120,7 +6058,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>False</t>
@@ -6156,15 +6093,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>4</v>
       </c>
@@ -6213,7 +6150,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>True</t>
@@ -6249,15 +6185,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>3</v>
       </c>
@@ -6347,15 +6283,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -6404,7 +6340,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>False</t>
@@ -6440,15 +6375,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6497,7 +6432,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6533,15 +6467,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>2</v>
       </c>
@@ -6590,7 +6524,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>False</t>
@@ -6626,15 +6559,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>4</v>
       </c>
@@ -6724,15 +6657,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>3</v>
       </c>
@@ -6822,15 +6755,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>4</v>
       </c>
@@ -6920,15 +6853,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>5</v>
       </c>
@@ -7018,15 +6951,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7116,15 +7049,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7174,7 +7107,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
           <t>False</t>
@@ -7210,15 +7142,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7268,7 +7200,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
           <t>False</t>
@@ -7304,15 +7235,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>5</v>
       </c>
@@ -7362,7 +7293,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
           <t>False</t>
@@ -7398,15 +7328,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7456,7 +7386,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>False</t>
@@ -7492,19 +7421,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
+          <t>視能訓練学</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7555,7 +7480,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
           <t>False</t>
@@ -7591,15 +7515,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>内分泌</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7648,7 +7572,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>False</t>
@@ -7687,12 +7610,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7741,7 +7664,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>True</t>
@@ -7777,15 +7699,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -7834,7 +7756,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7870,15 +7791,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7927,7 +7848,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>True</t>
@@ -7963,15 +7883,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -8020,7 +7940,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8056,15 +7975,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8113,7 +8032,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>False</t>
@@ -8149,15 +8067,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>1</v>
       </c>
@@ -8206,7 +8124,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>False</t>
@@ -8245,12 +8162,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>3</v>
       </c>
@@ -8299,7 +8216,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>True</t>
@@ -8338,12 +8254,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8392,7 +8308,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8431,12 +8346,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8485,7 +8400,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8521,15 +8435,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>4</v>
       </c>
@@ -8578,7 +8492,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>False</t>
@@ -8614,15 +8527,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>3</v>
       </c>
@@ -8671,7 +8584,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>False</t>
@@ -8707,15 +8619,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>1</v>
       </c>
@@ -8764,7 +8676,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>False</t>
@@ -8800,15 +8711,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>3</v>
       </c>
@@ -8857,7 +8768,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8893,15 +8803,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8950,7 +8860,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>False</t>
@@ -8986,15 +8895,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>4</v>
       </c>
@@ -9044,7 +8953,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>False</t>
@@ -9080,15 +8988,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -9137,7 +9045,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>False</t>
@@ -9173,15 +9080,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -9231,7 +9138,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>False</t>
@@ -9267,15 +9173,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>4</v>
       </c>
@@ -9324,7 +9230,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>False</t>
@@ -9360,15 +9265,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>3</v>
       </c>
@@ -9417,7 +9322,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>False</t>
@@ -9453,15 +9357,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>3</v>
       </c>
@@ -9510,7 +9414,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>False</t>
@@ -9546,15 +9449,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>4</v>
       </c>
@@ -9644,15 +9547,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>3</v>
       </c>
@@ -9701,7 +9604,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>True</t>
@@ -9737,15 +9639,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>4</v>
       </c>
@@ -9794,7 +9696,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>False</t>
@@ -9830,15 +9731,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9887,7 +9788,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>False</t>
@@ -9923,15 +9823,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>1</v>
       </c>
@@ -9980,7 +9880,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -10016,15 +9915,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>3</v>
       </c>
@@ -10073,7 +9972,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>True</t>
@@ -10109,15 +10007,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10166,7 +10064,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>False</t>
@@ -10202,15 +10099,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10259,7 +10156,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
           <t>False</t>
@@ -10295,15 +10191,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10352,7 +10248,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
           <t>False</t>
@@ -10388,15 +10283,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>2</v>
       </c>
@@ -10445,7 +10340,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>False</t>
@@ -10481,15 +10375,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10538,7 +10432,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>True</t>
@@ -10574,15 +10467,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>2</v>
       </c>
@@ -10631,7 +10524,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10670,12 +10562,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>2</v>
       </c>
@@ -10724,7 +10616,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>False</t>
@@ -10763,12 +10654,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>1</v>
       </c>
@@ -10817,7 +10708,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10853,15 +10743,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>3</v>
       </c>
@@ -10918,7 +10808,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>False</t>
@@ -10954,15 +10843,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -11011,7 +10900,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>False</t>
@@ -11047,15 +10935,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -11104,7 +10992,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>False</t>
@@ -11140,15 +11027,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11197,7 +11084,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>False</t>
@@ -11233,15 +11119,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11290,7 +11176,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>True</t>
@@ -11326,15 +11211,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>3</v>
       </c>
@@ -11383,7 +11268,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>False</t>
@@ -11419,15 +11303,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>3</v>
       </c>
@@ -11476,7 +11360,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>False</t>
@@ -11512,15 +11395,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>4</v>
       </c>
@@ -11569,7 +11452,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>False</t>
@@ -11605,15 +11487,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>3</v>
       </c>
@@ -11662,7 +11544,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>False</t>
@@ -11698,15 +11579,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11755,7 +11636,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>True</t>
@@ -11791,15 +11671,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>3</v>
       </c>
@@ -11848,7 +11728,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>True</t>
@@ -11884,15 +11763,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>3</v>
       </c>
@@ -11941,7 +11820,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>True</t>
@@ -11977,15 +11855,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>3</v>
       </c>
@@ -12034,7 +11912,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12070,15 +11947,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>5</v>
       </c>
@@ -12127,7 +12004,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12163,15 +12039,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>3</v>
       </c>
@@ -12220,7 +12096,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>False</t>
@@ -12256,15 +12131,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>3</v>
       </c>
@@ -12313,7 +12188,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>True</t>
@@ -12349,15 +12223,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>3</v>
       </c>
@@ -12406,7 +12280,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12442,15 +12315,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12499,7 +12372,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>False</t>
@@ -12535,15 +12407,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -12592,7 +12464,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>False</t>
@@ -12628,15 +12499,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12685,7 +12556,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>False</t>
@@ -12721,15 +12591,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>4</v>
       </c>
@@ -12778,7 +12648,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>True</t>
@@ -12814,15 +12683,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -12871,7 +12740,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>False</t>
@@ -12907,15 +12775,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12964,7 +12832,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>False</t>
@@ -13000,15 +12867,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>3</v>
       </c>
@@ -13057,7 +12924,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>True</t>
@@ -13093,15 +12959,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13150,7 +13016,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>True</t>
@@ -13186,15 +13051,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>3</v>
       </c>
@@ -13243,7 +13108,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>False</t>
@@ -13279,15 +13143,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>4</v>
       </c>
@@ -13377,15 +13241,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13434,7 +13298,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>False</t>
@@ -13470,15 +13333,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>2</v>
       </c>
@@ -13527,7 +13390,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>False</t>
@@ -13563,15 +13425,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>2</v>
       </c>
@@ -13620,7 +13482,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>False</t>
@@ -13656,15 +13517,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>3</v>
       </c>
@@ -13754,15 +13615,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>2</v>
       </c>
@@ -13851,15 +13712,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13908,7 +13769,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
           <t>True</t>
@@ -13944,15 +13804,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>5</v>
       </c>
@@ -14002,7 +13862,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
           <t>False</t>
@@ -14038,15 +13897,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>3</v>
       </c>
@@ -14136,15 +13995,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>4</v>
       </c>
@@ -14234,15 +14093,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>4</v>
       </c>
@@ -14332,15 +14191,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>4</v>
       </c>
@@ -14390,7 +14249,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
           <t>False</t>
@@ -14426,15 +14284,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>4</v>
       </c>
@@ -14484,7 +14342,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
           <t>True</t>
@@ -14520,15 +14377,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>3</v>
       </c>

--- a/CO国試data/CO_questions_2014.xlsx
+++ b/CO国試data/CO_questions_2014.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>個体の構造</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>個体の構造</t>
+          <t>細胞の構造と機能</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>遺伝</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>遺伝</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>視能障害のリハビリテーション</t>
+          <t>ロービジョン</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>病因と疾病の種類</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>眼位と眼球運動</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2567,12 +2567,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2941,12 +2941,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>中心フリッカ検査</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>前眼部、透光体検査</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>眼圧検査</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>病因と疾病の種類</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>涙器</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>ぶどう膜</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4333,12 +4333,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4425,12 +4425,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4517,12 +4517,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4609,12 +4609,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4793,12 +4793,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4977,12 +4977,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5253,12 +5253,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5351,12 +5351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5443,12 +5443,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5535,12 +5535,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5627,12 +5627,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5817,12 +5817,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6001,12 +6001,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6093,12 +6093,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>両眼視機能訓練</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6467,12 +6467,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6559,12 +6559,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6853,12 +6853,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6951,12 +6951,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7049,12 +7049,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7142,12 +7142,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7235,12 +7235,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7421,12 +7421,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>内分泌</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>内分泌</t>
+          <t>内分泌器官の構造と機能</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7607,12 +7607,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>疾病の原因</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7699,12 +7699,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の投与法</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7791,12 +7791,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7883,12 +7883,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7975,12 +7975,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8067,12 +8067,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼圧検査</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8343,12 +8343,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8435,12 +8435,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8527,12 +8527,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8619,12 +8619,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8711,12 +8711,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8803,12 +8803,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8895,12 +8895,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8988,12 +8988,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9080,12 +9080,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9173,12 +9173,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9449,12 +9449,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9547,12 +9547,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9823,12 +9823,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -10007,12 +10007,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10099,12 +10099,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10191,12 +10191,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10283,12 +10283,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10375,12 +10375,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10467,12 +10467,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10559,12 +10559,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>病因と疾病の種類</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10651,12 +10651,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10743,12 +10743,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10843,12 +10843,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>涙器</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10935,12 +10935,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11119,12 +11119,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11211,12 +11211,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11303,12 +11303,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11395,12 +11395,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11487,12 +11487,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11579,12 +11579,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11763,12 +11763,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11855,12 +11855,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11947,12 +11947,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12039,12 +12039,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12131,12 +12131,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼外傷</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12223,12 +12223,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12315,12 +12315,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12407,12 +12407,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12499,12 +12499,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12591,12 +12591,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12683,12 +12683,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12775,12 +12775,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12867,12 +12867,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12959,12 +12959,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13051,12 +13051,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>後天眼球運動障害のリハビリ</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13143,12 +13143,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>両眼視機能訓練</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13241,12 +13241,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>両眼視機能訓練</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13333,12 +13333,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13425,12 +13425,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13615,12 +13615,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13712,12 +13712,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13804,12 +13804,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -13995,12 +13995,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14093,12 +14093,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14191,12 +14191,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14284,12 +14284,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14377,12 +14377,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>角膜検査</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2014.xlsx
+++ b/CO国試data/CO_questions_2014.xlsx
@@ -550,7 +550,11 @@
           <t>細胞の構造と機能</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>細胞膜、核、ミトコンドリア</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -642,7 +646,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -734,7 +737,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>3</v>
       </c>
@@ -826,7 +828,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -918,7 +919,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1010,7 +1010,11 @@
           <t>遺伝子</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>染色体</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1102,7 +1106,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1194,7 +1197,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>3</v>
       </c>
@@ -1286,7 +1288,6 @@
           <t>ロービジョン</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>3</v>
       </c>
@@ -1378,7 +1379,11 @@
           <t>病因と疾病の種類</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>炎症、感染</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -1470,7 +1475,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>4</v>
       </c>
@@ -1562,7 +1571,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -1654,7 +1662,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1746,7 +1758,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>4</v>
       </c>
@@ -1838,7 +1849,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1930,7 +1940,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>4</v>
       </c>
@@ -2023,7 +2037,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2115,7 +2128,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2207,7 +2224,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2299,7 +2320,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>4</v>
       </c>
@@ -2391,7 +2416,11 @@
           <t>眼位と眼球運動</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>3</v>
       </c>
@@ -2483,7 +2512,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -2575,7 +2608,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>4</v>
       </c>
@@ -2667,7 +2699,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>3</v>
       </c>
@@ -2759,7 +2790,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2851,7 +2886,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>3</v>
       </c>
@@ -2949,7 +2983,6 @@
           <t>中心フリッカ検査</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3041,7 +3074,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>4</v>
       </c>
@@ -3139,7 +3176,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3231,7 +3272,11 @@
           <t>前眼部、透光体検査</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>細隙灯顕微鏡検査</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -3329,7 +3374,6 @@
           <t>眼圧検査</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -3421,7 +3465,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>4</v>
       </c>
@@ -3513,7 +3556,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>生体染色検査</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>3</v>
       </c>
@@ -3605,7 +3652,11 @@
           <t>病因と疾病の種類</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>免疫異常</t>
+        </is>
+      </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
@@ -3697,7 +3748,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>局所麻酔薬</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>2</v>
       </c>
@@ -3789,7 +3844,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H37" t="n">
         <v>4</v>
       </c>
@@ -3881,7 +3940,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3973,7 +4036,11 @@
           <t>涙器</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>鼻涙管閉塞</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4065,7 +4132,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -4157,7 +4223,11 @@
           <t>ぶどう膜</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ぶどう膜炎</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>3</v>
       </c>
@@ -4249,7 +4319,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>網膜色素変性、その他の変性およびジストロフィ</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4341,7 +4415,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4433,7 +4511,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>視神経症</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4525,7 +4607,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4617,7 +4703,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4709,7 +4799,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -4801,7 +4895,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4893,7 +4991,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -4985,7 +5087,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>4</v>
       </c>
@@ -5077,7 +5183,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -5169,7 +5279,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5261,7 +5375,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>4</v>
       </c>
@@ -5359,7 +5477,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>4</v>
       </c>
@@ -5451,7 +5573,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>4</v>
       </c>
@@ -5543,7 +5664,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>3</v>
       </c>
@@ -5635,7 +5755,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5733,7 +5857,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>2</v>
       </c>
@@ -5825,7 +5948,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5917,7 +6044,11 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -6009,7 +6140,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>4</v>
       </c>
@@ -6101,7 +6231,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>4</v>
       </c>
@@ -6193,7 +6322,11 @@
           <t>両眼視機能訓練</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>融像訓練</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>3</v>
       </c>
@@ -6291,7 +6424,11 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>適応と予後</t>
+        </is>
+      </c>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -6383,7 +6520,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6475,7 +6611,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>2</v>
       </c>
@@ -6567,7 +6702,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>瞳孔緊張症〈緊張性瞳孔〉</t>
+        </is>
+      </c>
       <c r="H67" t="n">
         <v>4</v>
       </c>
@@ -6665,7 +6804,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>3</v>
       </c>
@@ -6763,7 +6906,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>4</v>
       </c>
@@ -6861,7 +7008,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>5</v>
       </c>
@@ -6959,7 +7105,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7057,7 +7202,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7150,7 +7294,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7243,7 +7391,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>5</v>
       </c>
@@ -7336,7 +7483,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7429,7 +7575,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7523,7 +7673,11 @@
           <t>内分泌器官の構造と機能</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>副腎皮質</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -7615,7 +7769,6 @@
           <t>疾病の原因</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7707,7 +7860,11 @@
           <t>薬物の投与法</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>局所投与</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -7799,7 +7956,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7891,7 +8047,6 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -7983,7 +8138,11 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>倒像、直像鏡検査</t>
+        </is>
+      </c>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8075,7 +8234,6 @@
           <t>眼圧検査</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>1</v>
       </c>
@@ -8167,7 +8325,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>3</v>
       </c>
@@ -8259,7 +8416,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8351,7 +8507,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8443,7 +8598,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>遠視</t>
+        </is>
+      </c>
       <c r="H87" t="n">
         <v>4</v>
       </c>
@@ -8535,7 +8694,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>3</v>
       </c>
@@ -8627,7 +8785,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>1</v>
       </c>
@@ -8719,7 +8881,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>結像と収差</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>3</v>
       </c>
@@ -8811,7 +8977,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8903,7 +9068,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H92" t="n">
         <v>4</v>
       </c>
@@ -8996,7 +9165,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>屈折、調節の光学</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -9088,7 +9261,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -9181,7 +9353,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>4</v>
       </c>
@@ -9273,7 +9444,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>結像と収差</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>3</v>
       </c>
@@ -9365,7 +9540,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>3</v>
       </c>
@@ -9457,7 +9631,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H98" t="n">
         <v>4</v>
       </c>
@@ -9555,7 +9733,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H99" t="n">
         <v>3</v>
       </c>
@@ -9647,7 +9829,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>4</v>
       </c>
@@ -9739,7 +9925,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9831,7 +10021,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>1</v>
       </c>
@@ -9923,7 +10112,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>3</v>
       </c>
@@ -10015,7 +10203,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10107,7 +10294,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10199,7 +10390,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>瞳孔不同</t>
+        </is>
+      </c>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10291,7 +10486,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>涙液層破壊時間〈BUT〉</t>
+        </is>
+      </c>
       <c r="H107" t="n">
         <v>2</v>
       </c>
@@ -10383,7 +10582,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10475,7 +10673,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>点眼薬</t>
+        </is>
+      </c>
       <c r="H109" t="n">
         <v>2</v>
       </c>
@@ -10567,7 +10769,11 @@
           <t>病因と疾病の種類</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>炎症、感染</t>
+        </is>
+      </c>
       <c r="H110" t="n">
         <v>2</v>
       </c>
@@ -10659,7 +10865,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>1</v>
       </c>
@@ -10751,7 +10956,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>3</v>
       </c>
@@ -10851,7 +11055,11 @@
           <t>涙器</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>涙液分泌減少症、眼乾燥症〈ドライアイ〉</t>
+        </is>
+      </c>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10943,7 +11151,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>正常眼圧緑内障</t>
+        </is>
+      </c>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -11035,7 +11247,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11127,7 +11338,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>加齢黄斑変性</t>
+        </is>
+      </c>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11219,7 +11434,11 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>硝子体出血、混濁、後部硝子体剥離</t>
+        </is>
+      </c>
       <c r="H117" t="n">
         <v>3</v>
       </c>
@@ -11311,7 +11530,11 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>両眼開放視力検査</t>
+        </is>
+      </c>
       <c r="H118" t="n">
         <v>3</v>
       </c>
@@ -11403,7 +11626,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>4</v>
       </c>
@@ -11495,7 +11717,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H120" t="n">
         <v>3</v>
       </c>
@@ -11587,7 +11813,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11679,7 +11904,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>3</v>
       </c>
@@ -11771,7 +11995,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H123" t="n">
         <v>3</v>
       </c>
@@ -11863,7 +12091,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H124" t="n">
         <v>3</v>
       </c>
@@ -11955,7 +12187,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H125" t="n">
         <v>5</v>
       </c>
@@ -12047,7 +12283,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>3</v>
       </c>
@@ -12139,7 +12379,6 @@
           <t>眼外傷</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>3</v>
       </c>
@@ -12231,7 +12470,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H128" t="n">
         <v>3</v>
       </c>
@@ -12323,7 +12566,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12415,7 +12662,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -12507,7 +12758,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>微小斜視弱視</t>
+        </is>
+      </c>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12599,7 +12854,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H132" t="n">
         <v>4</v>
       </c>
@@ -12691,7 +12950,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>遮閉法</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -12783,7 +13046,11 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>適応と予後</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12875,7 +13142,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H135" t="n">
         <v>3</v>
       </c>
@@ -12967,7 +13238,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13059,7 +13329,6 @@
           <t>後天眼球運動障害のリハビリ</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>3</v>
       </c>
@@ -13151,7 +13420,6 @@
           <t>両眼視機能訓練</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>4</v>
       </c>
@@ -13249,7 +13517,11 @@
           <t>両眼視機能訓練</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>融像訓練</t>
+        </is>
+      </c>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13341,7 +13613,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>2</v>
       </c>
@@ -13433,7 +13704,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>屈折異常弱視</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>2</v>
       </c>
@@ -13525,7 +13800,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>3</v>
       </c>
@@ -13623,7 +13902,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>2</v>
       </c>
@@ -13720,7 +13998,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13812,7 +14089,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H145" t="n">
         <v>5</v>
       </c>
@@ -13905,7 +14186,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>3</v>
       </c>
@@ -14003,7 +14283,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H147" t="n">
         <v>4</v>
       </c>
@@ -14101,7 +14385,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>4</v>
       </c>
@@ -14199,7 +14482,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H149" t="n">
         <v>4</v>
       </c>
@@ -14292,7 +14579,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H150" t="n">
         <v>4</v>
       </c>
@@ -14385,7 +14676,11 @@
           <t>角膜検査</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>角膜形状解析、角膜トポグラフィ</t>
+        </is>
+      </c>
       <c r="H151" t="n">
         <v>3</v>
       </c>

--- a/CO国試data/CO_questions_2014.xlsx
+++ b/CO国試data/CO_questions_2014.xlsx
@@ -603,10 +603,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -694,10 +692,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -785,10 +781,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S4" t="b">
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -876,10 +870,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -967,10 +959,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S6" t="b">
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1063,10 +1053,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1154,10 +1142,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S8" t="b">
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1336,10 +1322,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S10" t="b">
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1432,10 +1416,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S11" t="b">
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1528,10 +1510,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1619,10 +1599,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1715,10 +1693,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1806,10 +1782,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1897,10 +1871,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1994,10 +1966,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2085,10 +2055,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2181,10 +2149,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2277,10 +2243,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S20" t="b">
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2373,10 +2337,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2565,10 +2527,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2656,10 +2616,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2747,10 +2705,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2843,10 +2799,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S26" t="b">
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2940,10 +2894,8 @@
           <t>2014_co_14_am026.jpg</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3031,10 +2983,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3133,10 +3083,8 @@
           <t>2014_co_14_am028.jpg</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S29" t="b">
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3229,10 +3177,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S30" t="b">
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3331,10 +3277,8 @@
           <t>2014_co_14_am030.jpg</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3422,10 +3366,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S32" t="b">
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3705,10 +3647,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3801,10 +3741,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S36" t="b">
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3897,10 +3835,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4089,10 +4025,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4180,10 +4114,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S40" t="b">
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4276,10 +4208,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4372,10 +4302,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S42" t="b">
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4468,10 +4396,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S43" t="b">
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4564,10 +4490,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S44" t="b">
+        <v>0</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4660,10 +4584,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4756,10 +4678,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S46" t="b">
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4852,10 +4772,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4948,10 +4866,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5044,10 +4960,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S49" t="b">
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5140,10 +5054,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S50" t="b">
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5236,10 +5148,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5332,10 +5242,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5434,10 +5342,8 @@
           <t>2014_co_14_am052.jpg</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S53" t="b">
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5530,10 +5436,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S54" t="b">
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5621,10 +5525,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S55" t="b">
+        <v>0</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5712,10 +5614,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S56" t="b">
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5905,10 +5805,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6001,10 +5899,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S59" t="b">
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6188,10 +6084,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S61" t="b">
+        <v>0</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6279,10 +6173,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S62" t="b">
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6381,10 +6273,8 @@
           <t>2014_co_14_am062（不備問題採点除外）.jpg</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S63" t="b">
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6477,10 +6367,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S64" t="b">
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6568,10 +6456,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6659,10 +6545,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6761,10 +6645,8 @@
           <t>2014_co_14_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6863,10 +6745,8 @@
           <t>2014_co_14_am067.jpg</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S68" t="b">
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7251,10 +7131,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S72" t="b">
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7348,10 +7226,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7440,10 +7316,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7532,10 +7406,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S75" t="b">
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7630,10 +7502,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7726,10 +7596,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7913,10 +7781,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8095,10 +7961,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8191,10 +8055,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8282,10 +8144,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S83" t="b">
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8464,10 +8324,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8555,10 +8413,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8651,10 +8507,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8742,10 +8596,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S88" t="b">
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8838,10 +8690,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8934,10 +8784,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9025,10 +8873,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9122,10 +8968,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9218,10 +9062,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9310,10 +9152,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S94" t="b">
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9401,10 +9241,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S95" t="b">
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9497,10 +9335,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9588,10 +9424,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S97" t="b">
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9882,10 +9716,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S100" t="b">
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -9978,10 +9810,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10069,10 +9899,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10251,10 +10079,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S104" t="b">
+        <v>0</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10347,10 +10173,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10443,10 +10267,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10539,10 +10361,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10726,10 +10546,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10822,10 +10640,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S110" t="b">
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10913,10 +10729,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11012,10 +10826,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S112" t="b">
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11108,10 +10920,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S113" t="b">
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11204,10 +11014,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S114" t="b">
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11295,10 +11103,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11487,10 +11293,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S117" t="b">
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11583,10 +11387,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S118" t="b">
+        <v>0</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -11674,10 +11476,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S119" t="b">
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11770,10 +11570,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S120" t="b">
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11952,10 +11750,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12144,10 +11940,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12240,10 +12034,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12336,10 +12128,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S126" t="b">
+        <v>0</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12523,10 +12313,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12619,10 +12407,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S129" t="b">
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12715,10 +12501,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12811,10 +12595,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13003,10 +12785,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S133" t="b">
+        <v>0</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13099,10 +12879,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S134" t="b">
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13377,10 +13155,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S137" t="b">
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13474,10 +13250,8 @@
           <t>2014_co_14_pm062.jpg</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S138" t="b">
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13570,10 +13344,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S139" t="b">
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13661,10 +13433,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S140" t="b">
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13757,10 +13527,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S141" t="b">
+        <v>0</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -13859,10 +13627,8 @@
           <t>2014_co_14_pm066.jpg</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -13955,10 +13721,8 @@
           <t>2014_co_14_pm067.jpg</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14143,10 +13907,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S145" t="b">
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14240,10 +14002,8 @@
           <t>2014_co_14_pm070.jpg</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S146" t="b">
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14342,10 +14102,8 @@
           <t>2014_co_14_pm071.jpg</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S147" t="b">
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14439,10 +14197,8 @@
           <t>2014_co_14_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S148" t="b">
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14536,10 +14292,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S149" t="b">
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -14735,10 +14489,8 @@
           <t>2014_co_14_pm075.jpg</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2014.xlsx
+++ b/CO国試data/CO_questions_2014.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1231,10 +1231,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S9" t="b">
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2324,7 +2322,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2338,7 +2336,7 @@
         </is>
       </c>
       <c r="S21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2418,7 +2416,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2431,10 +2429,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S22" t="b">
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3442,7 +3438,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3455,10 +3451,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S33" t="b">
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3538,7 +3532,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3551,10 +3545,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S34" t="b">
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3916,7 +3908,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3929,10 +3921,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S38" t="b">
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5696,7 +5686,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5714,10 +5704,8 @@
           <t>2014_co_14_am056.jpg</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S57" t="b">
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5980,7 +5968,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5993,10 +5981,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S60" t="b">
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6827,7 +6813,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6845,10 +6831,8 @@
           <t>2014_co_14_am068.jpg</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S69" t="b">
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6924,7 +6908,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6942,10 +6926,8 @@
           <t>2014_co_14_am069.jpg</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S70" t="b">
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7021,7 +7003,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7039,10 +7021,8 @@
           <t>2014_co_14_am070.jpg</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S71" t="b">
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7672,7 +7652,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7685,10 +7665,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S78" t="b">
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7857,7 +7835,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7870,10 +7848,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S80" t="b">
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8220,7 +8196,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -8233,10 +8209,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S84" t="b">
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9506,7 +9480,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -9524,10 +9498,8 @@
           <t>2014_co_14_pm022.jpg</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S98" t="b">
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9607,7 +9579,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -9620,10 +9592,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S99" t="b">
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9975,7 +9945,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9988,10 +9958,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S103" t="b">
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10437,7 +10405,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -10450,10 +10418,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S108" t="b">
+        <v>1</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11184,7 +11150,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -11197,10 +11163,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S116" t="b">
+        <v>1</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11646,7 +11610,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -11659,10 +11623,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S121" t="b">
+        <v>1</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -11831,7 +11793,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -11844,10 +11806,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S123" t="b">
+        <v>1</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12204,7 +12164,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -12217,10 +12177,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S127" t="b">
+        <v>1</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12676,7 +12634,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -12689,10 +12647,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S132" t="b">
+        <v>1</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -12960,7 +12916,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -12973,10 +12929,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S135" t="b">
+        <v>1</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13051,7 +13005,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -13064,10 +13018,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S136" t="b">
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13797,7 +13749,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -13810,10 +13762,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S144" t="b">
+        <v>1</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14374,7 +14324,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -14387,10 +14337,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S150" t="b">
+        <v>1</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
